--- a/Feuilles/Porte.xlsx
+++ b/Feuilles/Porte.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39940B1-8D1E-0F4A-A130-4582DF87B5D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A982C74-88A1-C742-948C-90A3D8BF207F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2600" yWindow="2960" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>MES</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>PONT</t>
+  </si>
+  <si>
+    <t>LOOP</t>
   </si>
 </sst>
 </file>
@@ -455,10 +458,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B34C31-2D9C-7940-9F39-E67ACD52E89F}">
-  <dimension ref="A1:D224"/>
+  <dimension ref="A1:E224"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -471,8 +474,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -486,7 +492,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -497,7 +503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -508,7 +514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -519,7 +525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -530,7 +536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -541,7 +547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -552,7 +558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -563,7 +569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -574,7 +580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -585,7 +591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -596,7 +602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -607,7 +613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -618,7 +624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -629,7 +635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>

--- a/Feuilles/Porte.xlsx
+++ b/Feuilles/Porte.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A982C74-88A1-C742-948C-90A3D8BF207F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E286CFB8-05B0-2C45-88B4-A40CFA55953F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2600" yWindow="2960" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
+    <workbookView xWindow="11700" yWindow="3260" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -646,7 +646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -657,7 +657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -668,7 +668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -681,8 +681,11 @@
       <c r="D19" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -693,7 +696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -704,7 +707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -715,7 +718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -726,7 +729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -737,7 +740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -748,7 +751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -759,7 +762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -769,8 +772,11 @@
       <c r="C27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -781,7 +787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -792,7 +798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -805,8 +811,11 @@
       <c r="D30" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -817,7 +826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -828,7 +837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -839,7 +848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -850,7 +859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -861,7 +870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -872,7 +881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -883,7 +892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -894,7 +903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -905,7 +914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -916,7 +925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -927,7 +936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -938,7 +947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -949,7 +958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -960,7 +969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -971,7 +980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -982,7 +991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -995,8 +1004,11 @@
       <c r="D47" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1007,7 +1019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1018,7 +1030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1029,7 +1041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1040,7 +1052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1051,7 +1063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1062,7 +1074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1073,7 +1085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1086,8 +1098,11 @@
       <c r="D55" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1098,7 +1113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1109,7 +1124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1120,7 +1135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1131,7 +1146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1142,7 +1157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1153,7 +1168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1164,7 +1179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1177,8 +1192,11 @@
       <c r="D63" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1368,7 +1386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -1379,7 +1397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -1390,7 +1408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -1401,7 +1419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -1412,7 +1430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -1423,7 +1441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -1434,7 +1452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -1445,7 +1463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -1456,7 +1474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -1467,7 +1485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -1478,7 +1496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -1491,8 +1509,11 @@
       <c r="D91" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -1503,7 +1524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -1514,7 +1535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -1525,7 +1546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -1536,7 +1557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
@@ -1547,7 +1568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -1558,7 +1579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -1569,7 +1590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -1582,8 +1603,11 @@
       <c r="D99" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>99</v>
       </c>
@@ -1594,7 +1618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>100</v>
       </c>
@@ -1605,7 +1629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>101</v>
       </c>
@@ -1616,7 +1640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>102</v>
       </c>
@@ -1627,7 +1651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>103</v>
       </c>
@@ -1638,7 +1662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>104</v>
       </c>
@@ -1649,7 +1673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>105</v>
       </c>
@@ -1660,7 +1684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>106</v>
       </c>
@@ -1673,8 +1697,11 @@
       <c r="D107" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>107</v>
       </c>
@@ -1685,7 +1712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>108</v>
       </c>
@@ -1696,7 +1723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>109</v>
       </c>
@@ -1707,7 +1734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>110</v>
       </c>
@@ -1718,7 +1745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>111</v>
       </c>
@@ -1729,7 +1756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>112</v>
       </c>
@@ -1740,7 +1767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>113</v>
       </c>
@@ -1751,7 +1778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>114</v>
       </c>
@@ -1761,8 +1788,11 @@
       <c r="C115">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>115</v>
       </c>
@@ -1773,7 +1803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>116</v>
       </c>
@@ -1784,7 +1814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>117</v>
       </c>
@@ -1795,7 +1825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>118</v>
       </c>
@@ -1806,7 +1836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>119</v>
       </c>
@@ -1817,7 +1847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>120</v>
       </c>
@@ -1828,7 +1858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>121</v>
       </c>
@@ -1839,7 +1869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>122</v>
       </c>
@@ -1849,8 +1879,11 @@
       <c r="C123">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>123</v>
       </c>
@@ -1861,7 +1894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>124</v>
       </c>
@@ -1872,7 +1905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>125</v>
       </c>
@@ -1886,7 +1919,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>126</v>
       </c>
@@ -1897,7 +1930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>127</v>
       </c>
